--- a/public/assets/template/pengundian-tgr-template.xlsx
+++ b/public/assets/template/pengundian-tgr-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndejo\Documents\GitHub\simaps-ukasya\public\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D71ABFC-0107-45AC-94CA-6EC1EA461BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B873DA-EA28-4F75-924D-CF9651E2AD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{51F6D04B-38A7-4907-901E-8D2AF0D93E74}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="15375" windowHeight="7875" xr2:uid="{51F6D04B-38A7-4907-901E-8D2AF0D93E74}"/>
   </bookViews>
   <sheets>
     <sheet name="Lembar1" sheetId="1" r:id="rId1"/>
@@ -34,54 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>Nama</t>
+    <t>Atlet_ID</t>
   </si>
   <si>
-    <t>Golongan</t>
-  </si>
-  <si>
-    <t>Jenis Kelamin</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Ukasya</t>
-  </si>
-  <si>
-    <t>Remaja</t>
-  </si>
-  <si>
-    <t>Pra Remaja</t>
-  </si>
-  <si>
-    <t>Dewasa</t>
-  </si>
-  <si>
-    <t>Kelas A</t>
-  </si>
-  <si>
-    <t>No Undian</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Kelas B</t>
-  </si>
-  <si>
-    <t>Kelas C</t>
-  </si>
-  <si>
-    <t>Kontingen</t>
-  </si>
-  <si>
-    <t>ASAD</t>
-  </si>
-  <si>
-    <t>Kelas_Kategori</t>
+    <t>No_Undian</t>
   </si>
 </sst>
 </file>
@@ -474,135 +432,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A86521A1-DC6B-4F40-AA0D-147BEF52CF9B}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B5" s="1">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="B6" s="1">
         <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="1">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
